--- a/docs/FEATURE_STATUS.xlsx
+++ b/docs/FEATURE_STATUS.xlsx
@@ -45,7 +45,7 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -97,6 +97,11 @@
         <fgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCEFC7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -124,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -162,6 +167,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -783,11 +791,19 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
+      <c r="K4" s="15" t="inlineStr">
+        <is>
+          <t>F4 (data quality, found in live Spider-Man run): feed summaries with HTML (e.g. Google News) were stored as raw &lt;a&gt; markup instead of readable text.</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Added _plain_text() to strip tags + unescape entities; applied to RSS title/excerpt/author.</t>
+        </is>
+      </c>
       <c r="M4" s="13" t="inlineStr">
         <is>
-          <t>PASS (re-verified green)</t>
+          <t>PASS (live re-run shows clean headlines; test_feed_html_is_reduced_to_readable_text)</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6226,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
@@ -6311,8 +6326,6 @@
         <v/>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>

--- a/docs/FEATURE_STATUS.xlsx
+++ b/docs/FEATURE_STATUS.xlsx
@@ -537,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M95"/>
+  <dimension ref="A1:M99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6197,6 +6197,258 @@
       <c r="M95" s="13" t="inlineStr">
         <is>
           <t>PASS (http probe green; test_active_sessions_panel_is_wired_in_the_ui)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>US-095</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>Sessions</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Trust a domain (standing consent)</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>capture.trust_domain</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>As a researcher, I approve a domain once so future capture sessions on it start hands-free.</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Records per-client standing consent; requires approved_by_user + Chrome host permission; revocable and audited.</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Extension settings 'Trust domain' / 'Always capture this domain'</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Bare public domain only; scheme/port/IP/localhost rejected.</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>Documented</t>
+        </is>
+      </c>
+      <c r="J96" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>Built this session</t>
+        </is>
+      </c>
+      <c r="M96" s="13" t="inlineStr">
+        <is>
+          <t>PASS (test_trusted_domain_auto_approves_only_matching_sessions; test_standing_consent_trusts_domain_and_auto_approves; JS syntax-checked + core tests)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>US-096</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>Sessions</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>List/revoke trusted domains</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>capture.list_trusted_domains</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>As a researcher, I see and remove the domains I've trusted.</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Lists active trusted domains; untrust revokes and stops future auto-approval; unpair clears all.</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Extension settings list + Remove</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Per-client; cascade-cleared on client delete.</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>Documented</t>
+        </is>
+      </c>
+      <c r="J97" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>Built this session</t>
+        </is>
+      </c>
+      <c r="M97" s="13" t="inlineStr">
+        <is>
+          <t>PASS (test_trusted_domain_auto_approves_only_matching_sessions; test_standing_consent_trusts_domain_and_auto_approves; JS syntax-checked + core tests)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>US-097</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>Sessions</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Auto-approve trusted sessions</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>capture.auto_approve_for_client</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>As a researcher, requested sessions on my trusted domains approve automatically.</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Approves only requested sessions whose domain the client trusts; each keeps its own 30-min TTL; audited as standing_consent.</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Extension auto-approve poll (1 min) + popup open</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Untrusted-domain sessions stay 'requested'; never opens/navigates tabs.</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>Documented</t>
+        </is>
+      </c>
+      <c r="J98" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>Built this session</t>
+        </is>
+      </c>
+      <c r="M98" s="13" t="inlineStr">
+        <is>
+          <t>PASS (test_trusted_domain_auto_approves_only_matching_sessions; test_standing_consent_trusts_domain_and_auto_approves; JS syntax-checked + core tests)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>US-098</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>Sessions</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Standing-consent recording</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>background.autoApproveTick + startTrustedSession</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>As a researcher, capture starts on trusted domains on tabs I already have open.</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Poll approves + injects recorder into open tabs on the domain; onUpdated re-injects on navigation; Stop/TTL still apply.</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>automatic while browsing a trusted domain</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Never headless/unattended; blocked while collection stopped; permission kept until untrust.</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>Documented</t>
+        </is>
+      </c>
+      <c r="J99" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>Built this session</t>
+        </is>
+      </c>
+      <c r="M99" s="13" t="inlineStr">
+        <is>
+          <t>PASS (test_trusted_domain_auto_approves_only_matching_sessions; test_standing_consent_trusts_domain_and_auto_approves; JS syntax-checked + core tests)</t>
         </is>
       </c>
     </row>
@@ -6226,6 +6478,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
@@ -6245,7 +6498,7 @@
         </is>
       </c>
       <c r="B4" s="12">
-        <f>COUNTA('User Stories'!A2:A95)</f>
+        <f>COUNTA('User Stories'!A2:A99)</f>
         <v/>
       </c>
     </row>
@@ -6256,7 +6509,7 @@
         </is>
       </c>
       <c r="B5" s="12">
-        <f>COUNTIF('User Stories'!I2:I95,"Documented")</f>
+        <f>COUNTIF('User Stories'!I2:I99,"Documented")</f>
         <v/>
       </c>
     </row>
@@ -6267,7 +6520,7 @@
         </is>
       </c>
       <c r="B6" s="12">
-        <f>COUNTIF('User Stories'!J2:J95,"?*")</f>
+        <f>COUNTIF('User Stories'!J2:J99,"?*")</f>
         <v/>
       </c>
     </row>
@@ -6278,7 +6531,7 @@
         </is>
       </c>
       <c r="B7" s="12">
-        <f>COUNTIF('User Stories'!J2:J95,"PASS*")</f>
+        <f>COUNTIF('User Stories'!J2:J99,"PASS*")</f>
         <v/>
       </c>
     </row>
@@ -6289,7 +6542,7 @@
         </is>
       </c>
       <c r="B8" s="12">
-        <f>COUNTIF('User Stories'!J2:J95,"FAIL*")</f>
+        <f>COUNTIF('User Stories'!J2:J99,"FAIL*")</f>
         <v/>
       </c>
     </row>
@@ -6300,7 +6553,7 @@
         </is>
       </c>
       <c r="B9" s="12">
-        <f>COUNTIF('User Stories'!K2:K95,"?*")</f>
+        <f>COUNTIF('User Stories'!K2:K99,"?*")</f>
         <v/>
       </c>
     </row>
@@ -6311,7 +6564,7 @@
         </is>
       </c>
       <c r="B10" s="12">
-        <f>COUNTIF('User Stories'!L2:L95,"?*")</f>
+        <f>COUNTIF('User Stories'!L2:L99,"?*")</f>
         <v/>
       </c>
     </row>
@@ -6322,10 +6575,12 @@
         </is>
       </c>
       <c r="B11" s="12">
-        <f>COUNTIF('User Stories'!M2:M95,"PASS*")</f>
+        <f>COUNTIF('User Stories'!M2:M99,"PASS*")</f>
         <v/>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
@@ -6345,7 +6600,7 @@
         </is>
       </c>
       <c r="B15" s="12">
-        <f>COUNTIF('User Stories'!B2:B95,"Research MCP")</f>
+        <f>COUNTIF('User Stories'!B2:B99,"Research MCP")</f>
         <v/>
       </c>
     </row>
@@ -6356,7 +6611,7 @@
         </is>
       </c>
       <c r="B16" s="12">
-        <f>COUNTIF('User Stories'!B2:B95,"Planner")</f>
+        <f>COUNTIF('User Stories'!B2:B99,"Planner")</f>
         <v/>
       </c>
     </row>
@@ -6367,7 +6622,7 @@
         </is>
       </c>
       <c r="B17" s="12">
-        <f>COUNTIF('User Stories'!B2:B95,"Store")</f>
+        <f>COUNTIF('User Stories'!B2:B99,"Store")</f>
         <v/>
       </c>
     </row>
@@ -6378,7 +6633,7 @@
         </is>
       </c>
       <c r="B18" s="12">
-        <f>COUNTIF('User Stories'!B2:B95,"Connectors")</f>
+        <f>COUNTIF('User Stories'!B2:B99,"Connectors")</f>
         <v/>
       </c>
     </row>
@@ -6389,7 +6644,7 @@
         </is>
       </c>
       <c r="B19" s="12">
-        <f>COUNTIF('User Stories'!B2:B95,"Export")</f>
+        <f>COUNTIF('User Stories'!B2:B99,"Export")</f>
         <v/>
       </c>
     </row>
@@ -6400,7 +6655,7 @@
         </is>
       </c>
       <c r="B20" s="12">
-        <f>COUNTIF('User Stories'!B2:B95,"Capture")</f>
+        <f>COUNTIF('User Stories'!B2:B99,"Capture")</f>
         <v/>
       </c>
     </row>
@@ -6411,7 +6666,7 @@
         </is>
       </c>
       <c r="B21" s="12">
-        <f>COUNTIF('User Stories'!B2:B95,"Sessions")</f>
+        <f>COUNTIF('User Stories'!B2:B99,"Sessions")</f>
         <v/>
       </c>
     </row>
@@ -6422,7 +6677,7 @@
         </is>
       </c>
       <c r="B22" s="12">
-        <f>COUNTIF('User Stories'!B2:B95,"CLI")</f>
+        <f>COUNTIF('User Stories'!B2:B99,"CLI")</f>
         <v/>
       </c>
     </row>
@@ -6433,7 +6688,7 @@
         </is>
       </c>
       <c r="B23" s="12">
-        <f>COUNTIF('User Stories'!B2:B95,"Collectors")</f>
+        <f>COUNTIF('User Stories'!B2:B99,"Collectors")</f>
         <v/>
       </c>
     </row>
@@ -6444,7 +6699,7 @@
         </is>
       </c>
       <c r="B24" s="12">
-        <f>COUNTIF('User Stories'!B2:B95,"Reporting")</f>
+        <f>COUNTIF('User Stories'!B2:B99,"Reporting")</f>
         <v/>
       </c>
     </row>
@@ -6455,7 +6710,7 @@
         </is>
       </c>
       <c r="B25" s="12">
-        <f>COUNTIF('User Stories'!B2:B95,"Config")</f>
+        <f>COUNTIF('User Stories'!B2:B99,"Config")</f>
         <v/>
       </c>
     </row>
@@ -6466,7 +6721,7 @@
         </is>
       </c>
       <c r="B26" s="12">
-        <f>COUNTIF('User Stories'!B2:B95,"Control Center")</f>
+        <f>COUNTIF('User Stories'!B2:B99,"Control Center")</f>
         <v/>
       </c>
     </row>
@@ -6477,7 +6732,7 @@
         </is>
       </c>
       <c r="B27" s="12">
-        <f>COUNTIF('User Stories'!B2:B95,"Extension Options")</f>
+        <f>COUNTIF('User Stories'!B2:B99,"Extension Options")</f>
         <v/>
       </c>
     </row>
@@ -6488,7 +6743,7 @@
         </is>
       </c>
       <c r="B28" s="12">
-        <f>COUNTIF('User Stories'!B2:B95,"Extension Popup")</f>
+        <f>COUNTIF('User Stories'!B2:B99,"Extension Popup")</f>
         <v/>
       </c>
     </row>
@@ -6499,7 +6754,7 @@
         </is>
       </c>
       <c r="B29" s="12">
-        <f>COUNTIF('User Stories'!B2:B95,"Extension Background")</f>
+        <f>COUNTIF('User Stories'!B2:B99,"Extension Background")</f>
         <v/>
       </c>
     </row>
@@ -6510,7 +6765,7 @@
         </is>
       </c>
       <c r="B30" s="12">
-        <f>COUNTIF('User Stories'!B2:B95,"Launcher")</f>
+        <f>COUNTIF('User Stories'!B2:B99,"Launcher")</f>
         <v/>
       </c>
     </row>

--- a/docs/FEATURE_STATUS.xlsx
+++ b/docs/FEATURE_STATUS.xlsx
@@ -537,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M99"/>
+  <dimension ref="A1:M100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6449,6 +6449,69 @@
       <c r="M99" s="13" t="inlineStr">
         <is>
           <t>PASS (test_trusted_domain_auto_approves_only_matching_sessions; test_standing_consent_trusts_domain_and_auto_approves; JS syntax-checked + core tests)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>US-099</t>
+        </is>
+      </c>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>Launcher</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>One-line installer</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>install.sh</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>As a new user, I install everything with a single pasted command.</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>curl|bash: clones repo, installs Python+Postgres if missing (macOS brew / Linux apt), creates+migrates db, writes .env, attaches MCP to Claude/Codex, opens dashboard. Idempotent; never overwrites .env/db.</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>curl -fsSL .../install.sh | bash</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>macOS needs Homebrew; runs as root or via sudo; OYSTER_HOME/BRANCH/REPO overridable; extension still loaded once manually.</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>Documented</t>
+        </is>
+      </c>
+      <c r="J100" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>Built this session</t>
+        </is>
+      </c>
+      <c r="M100" s="13" t="inlineStr">
+        <is>
+          <t>PASS (ran end-to-end in a clean temp location: clone-&gt;db-&gt;migrate-&gt;attach-&gt;exit 0; bash -n clean)</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6561,7 @@
         </is>
       </c>
       <c r="B4" s="12">
-        <f>COUNTA('User Stories'!A2:A99)</f>
+        <f>COUNTA('User Stories'!A2:A100)</f>
         <v/>
       </c>
     </row>
@@ -6509,7 +6572,7 @@
         </is>
       </c>
       <c r="B5" s="12">
-        <f>COUNTIF('User Stories'!I2:I99,"Documented")</f>
+        <f>COUNTIF('User Stories'!I2:I100,"Documented")</f>
         <v/>
       </c>
     </row>
@@ -6520,7 +6583,7 @@
         </is>
       </c>
       <c r="B6" s="12">
-        <f>COUNTIF('User Stories'!J2:J99,"?*")</f>
+        <f>COUNTIF('User Stories'!J2:J100,"?*")</f>
         <v/>
       </c>
     </row>
@@ -6531,7 +6594,7 @@
         </is>
       </c>
       <c r="B7" s="12">
-        <f>COUNTIF('User Stories'!J2:J99,"PASS*")</f>
+        <f>COUNTIF('User Stories'!J2:J100,"PASS*")</f>
         <v/>
       </c>
     </row>
@@ -6542,7 +6605,7 @@
         </is>
       </c>
       <c r="B8" s="12">
-        <f>COUNTIF('User Stories'!J2:J99,"FAIL*")</f>
+        <f>COUNTIF('User Stories'!J2:J100,"FAIL*")</f>
         <v/>
       </c>
     </row>
@@ -6553,7 +6616,7 @@
         </is>
       </c>
       <c r="B9" s="12">
-        <f>COUNTIF('User Stories'!K2:K99,"?*")</f>
+        <f>COUNTIF('User Stories'!K2:K100,"?*")</f>
         <v/>
       </c>
     </row>
@@ -6564,7 +6627,7 @@
         </is>
       </c>
       <c r="B10" s="12">
-        <f>COUNTIF('User Stories'!L2:L99,"?*")</f>
+        <f>COUNTIF('User Stories'!L2:L100,"?*")</f>
         <v/>
       </c>
     </row>
@@ -6575,7 +6638,7 @@
         </is>
       </c>
       <c r="B11" s="12">
-        <f>COUNTIF('User Stories'!M2:M99,"PASS*")</f>
+        <f>COUNTIF('User Stories'!M2:M100,"PASS*")</f>
         <v/>
       </c>
     </row>
@@ -6600,7 +6663,7 @@
         </is>
       </c>
       <c r="B15" s="12">
-        <f>COUNTIF('User Stories'!B2:B99,"Research MCP")</f>
+        <f>COUNTIF('User Stories'!B2:B100,"Research MCP")</f>
         <v/>
       </c>
     </row>
@@ -6611,7 +6674,7 @@
         </is>
       </c>
       <c r="B16" s="12">
-        <f>COUNTIF('User Stories'!B2:B99,"Planner")</f>
+        <f>COUNTIF('User Stories'!B2:B100,"Planner")</f>
         <v/>
       </c>
     </row>
@@ -6622,7 +6685,7 @@
         </is>
       </c>
       <c r="B17" s="12">
-        <f>COUNTIF('User Stories'!B2:B99,"Store")</f>
+        <f>COUNTIF('User Stories'!B2:B100,"Store")</f>
         <v/>
       </c>
     </row>
@@ -6633,7 +6696,7 @@
         </is>
       </c>
       <c r="B18" s="12">
-        <f>COUNTIF('User Stories'!B2:B99,"Connectors")</f>
+        <f>COUNTIF('User Stories'!B2:B100,"Connectors")</f>
         <v/>
       </c>
     </row>
@@ -6644,7 +6707,7 @@
         </is>
       </c>
       <c r="B19" s="12">
-        <f>COUNTIF('User Stories'!B2:B99,"Export")</f>
+        <f>COUNTIF('User Stories'!B2:B100,"Export")</f>
         <v/>
       </c>
     </row>
@@ -6655,7 +6718,7 @@
         </is>
       </c>
       <c r="B20" s="12">
-        <f>COUNTIF('User Stories'!B2:B99,"Capture")</f>
+        <f>COUNTIF('User Stories'!B2:B100,"Capture")</f>
         <v/>
       </c>
     </row>
@@ -6666,7 +6729,7 @@
         </is>
       </c>
       <c r="B21" s="12">
-        <f>COUNTIF('User Stories'!B2:B99,"Sessions")</f>
+        <f>COUNTIF('User Stories'!B2:B100,"Sessions")</f>
         <v/>
       </c>
     </row>
@@ -6677,7 +6740,7 @@
         </is>
       </c>
       <c r="B22" s="12">
-        <f>COUNTIF('User Stories'!B2:B99,"CLI")</f>
+        <f>COUNTIF('User Stories'!B2:B100,"CLI")</f>
         <v/>
       </c>
     </row>
@@ -6688,7 +6751,7 @@
         </is>
       </c>
       <c r="B23" s="12">
-        <f>COUNTIF('User Stories'!B2:B99,"Collectors")</f>
+        <f>COUNTIF('User Stories'!B2:B100,"Collectors")</f>
         <v/>
       </c>
     </row>
@@ -6699,7 +6762,7 @@
         </is>
       </c>
       <c r="B24" s="12">
-        <f>COUNTIF('User Stories'!B2:B99,"Reporting")</f>
+        <f>COUNTIF('User Stories'!B2:B100,"Reporting")</f>
         <v/>
       </c>
     </row>
@@ -6710,7 +6773,7 @@
         </is>
       </c>
       <c r="B25" s="12">
-        <f>COUNTIF('User Stories'!B2:B99,"Config")</f>
+        <f>COUNTIF('User Stories'!B2:B100,"Config")</f>
         <v/>
       </c>
     </row>
@@ -6721,7 +6784,7 @@
         </is>
       </c>
       <c r="B26" s="12">
-        <f>COUNTIF('User Stories'!B2:B99,"Control Center")</f>
+        <f>COUNTIF('User Stories'!B2:B100,"Control Center")</f>
         <v/>
       </c>
     </row>
@@ -6732,7 +6795,7 @@
         </is>
       </c>
       <c r="B27" s="12">
-        <f>COUNTIF('User Stories'!B2:B99,"Extension Options")</f>
+        <f>COUNTIF('User Stories'!B2:B100,"Extension Options")</f>
         <v/>
       </c>
     </row>
@@ -6743,7 +6806,7 @@
         </is>
       </c>
       <c r="B28" s="12">
-        <f>COUNTIF('User Stories'!B2:B99,"Extension Popup")</f>
+        <f>COUNTIF('User Stories'!B2:B100,"Extension Popup")</f>
         <v/>
       </c>
     </row>
@@ -6754,7 +6817,7 @@
         </is>
       </c>
       <c r="B29" s="12">
-        <f>COUNTIF('User Stories'!B2:B99,"Extension Background")</f>
+        <f>COUNTIF('User Stories'!B2:B100,"Extension Background")</f>
         <v/>
       </c>
     </row>
@@ -6765,7 +6828,7 @@
         </is>
       </c>
       <c r="B30" s="12">
-        <f>COUNTIF('User Stories'!B2:B99,"Launcher")</f>
+        <f>COUNTIF('User Stories'!B2:B100,"Launcher")</f>
         <v/>
       </c>
     </row>

--- a/docs/FEATURE_STATUS.xlsx
+++ b/docs/FEATURE_STATUS.xlsx
@@ -537,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M100"/>
+  <dimension ref="A1:M104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6512,6 +6512,258 @@
       <c r="M100" s="13" t="inlineStr">
         <is>
           <t>PASS (ran end-to-end in a clean temp location: clone-&gt;db-&gt;migrate-&gt;attach-&gt;exit 0; bash -n clean)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>US-100</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>Control Center</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>First-run onboarding</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>control_center.onboarding</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>As a new user, the dashboard explains how the parts fit and what to do first.</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>A 'Welcome — start here' panel shows the AI-host/dashboard/extension model and a live checklist (DB, attach host, first research, browser capture); dismissible.</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>opens automatically on first dashboard load</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>Hidden after 'Hide this' (localStorage).</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>Documented</t>
+        </is>
+      </c>
+      <c r="J101" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>Built this session</t>
+        </is>
+      </c>
+      <c r="M101" s="13" t="inlineStr">
+        <is>
+          <t>PASS (server + endpoints tested; dashboard rendered live; JS syntax-checked + core tests)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>US-101</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>Control Center</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Guided browser-capture setup</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>control_center.capture-setup-panel</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>As a new user, the dashboard walks me from install to a running capture.</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Numbered panel: exact Load-unpacked folder path (with Copy), pairing code, and live paired/not-paired status.</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>'Set up browser capture' panel</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>extension_path + browser_paired from /api/status.</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>Documented</t>
+        </is>
+      </c>
+      <c r="J102" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>Built this session</t>
+        </is>
+      </c>
+      <c r="M102" s="13" t="inlineStr">
+        <is>
+          <t>PASS (server + endpoints tested; dashboard rendered live; JS syntax-checked + core tests)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>US-102</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>Sessions</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Human-initiated capture start</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>capture.start_session</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>As a researcher, I start a capture myself with one click, no agent needed.</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>start_session creates+approves a session in one step; POST /api/capture/sessions/start requires approved_by_user.</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>extension popup 'Start capturing this site'</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>Consent-gated; domain validated; 30-min TTL.</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>Documented</t>
+        </is>
+      </c>
+      <c r="J103" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>Built this session</t>
+        </is>
+      </c>
+      <c r="M103" s="13" t="inlineStr">
+        <is>
+          <t>PASS (server + endpoints tested; dashboard rendered live; JS syntax-checked + core tests)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>US-103</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>Extension Popup</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Start/Stop on-switch + status</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>popup.renderCaptureNow + startCaptureThisSite</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>As a researcher, the popup shows Off/Recording and lets me start on the current site.</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Capture pill Off/Recording; 'Start capturing &lt;domain&gt;' for the active tab + selected job; requests Chrome permission then starts.</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>extension popup</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Needs a job selected and an http(s) tab; Stop via active-session card.</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>Documented</t>
+        </is>
+      </c>
+      <c r="J104" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>Built this session</t>
+        </is>
+      </c>
+      <c r="M104" s="13" t="inlineStr">
+        <is>
+          <t>PASS (server + endpoints tested; dashboard rendered live; JS syntax-checked + core tests)</t>
         </is>
       </c>
     </row>
@@ -6561,7 +6813,7 @@
         </is>
       </c>
       <c r="B4" s="12">
-        <f>COUNTA('User Stories'!A2:A100)</f>
+        <f>COUNTA('User Stories'!A2:A104)</f>
         <v/>
       </c>
     </row>
@@ -6572,7 +6824,7 @@
         </is>
       </c>
       <c r="B5" s="12">
-        <f>COUNTIF('User Stories'!I2:I100,"Documented")</f>
+        <f>COUNTIF('User Stories'!I2:I104,"Documented")</f>
         <v/>
       </c>
     </row>
@@ -6583,7 +6835,7 @@
         </is>
       </c>
       <c r="B6" s="12">
-        <f>COUNTIF('User Stories'!J2:J100,"?*")</f>
+        <f>COUNTIF('User Stories'!J2:J104,"?*")</f>
         <v/>
       </c>
     </row>
@@ -6594,7 +6846,7 @@
         </is>
       </c>
       <c r="B7" s="12">
-        <f>COUNTIF('User Stories'!J2:J100,"PASS*")</f>
+        <f>COUNTIF('User Stories'!J2:J104,"PASS*")</f>
         <v/>
       </c>
     </row>
@@ -6605,7 +6857,7 @@
         </is>
       </c>
       <c r="B8" s="12">
-        <f>COUNTIF('User Stories'!J2:J100,"FAIL*")</f>
+        <f>COUNTIF('User Stories'!J2:J104,"FAIL*")</f>
         <v/>
       </c>
     </row>
@@ -6616,7 +6868,7 @@
         </is>
       </c>
       <c r="B9" s="12">
-        <f>COUNTIF('User Stories'!K2:K100,"?*")</f>
+        <f>COUNTIF('User Stories'!K2:K104,"?*")</f>
         <v/>
       </c>
     </row>
@@ -6627,7 +6879,7 @@
         </is>
       </c>
       <c r="B10" s="12">
-        <f>COUNTIF('User Stories'!L2:L100,"?*")</f>
+        <f>COUNTIF('User Stories'!L2:L104,"?*")</f>
         <v/>
       </c>
     </row>
@@ -6638,7 +6890,7 @@
         </is>
       </c>
       <c r="B11" s="12">
-        <f>COUNTIF('User Stories'!M2:M100,"PASS*")</f>
+        <f>COUNTIF('User Stories'!M2:M104,"PASS*")</f>
         <v/>
       </c>
     </row>
@@ -6663,7 +6915,7 @@
         </is>
       </c>
       <c r="B15" s="12">
-        <f>COUNTIF('User Stories'!B2:B100,"Research MCP")</f>
+        <f>COUNTIF('User Stories'!B2:B104,"Research MCP")</f>
         <v/>
       </c>
     </row>
@@ -6674,7 +6926,7 @@
         </is>
       </c>
       <c r="B16" s="12">
-        <f>COUNTIF('User Stories'!B2:B100,"Planner")</f>
+        <f>COUNTIF('User Stories'!B2:B104,"Planner")</f>
         <v/>
       </c>
     </row>
@@ -6685,7 +6937,7 @@
         </is>
       </c>
       <c r="B17" s="12">
-        <f>COUNTIF('User Stories'!B2:B100,"Store")</f>
+        <f>COUNTIF('User Stories'!B2:B104,"Store")</f>
         <v/>
       </c>
     </row>
@@ -6696,7 +6948,7 @@
         </is>
       </c>
       <c r="B18" s="12">
-        <f>COUNTIF('User Stories'!B2:B100,"Connectors")</f>
+        <f>COUNTIF('User Stories'!B2:B104,"Connectors")</f>
         <v/>
       </c>
     </row>
@@ -6707,7 +6959,7 @@
         </is>
       </c>
       <c r="B19" s="12">
-        <f>COUNTIF('User Stories'!B2:B100,"Export")</f>
+        <f>COUNTIF('User Stories'!B2:B104,"Export")</f>
         <v/>
       </c>
     </row>
@@ -6718,7 +6970,7 @@
         </is>
       </c>
       <c r="B20" s="12">
-        <f>COUNTIF('User Stories'!B2:B100,"Capture")</f>
+        <f>COUNTIF('User Stories'!B2:B104,"Capture")</f>
         <v/>
       </c>
     </row>
@@ -6729,7 +6981,7 @@
         </is>
       </c>
       <c r="B21" s="12">
-        <f>COUNTIF('User Stories'!B2:B100,"Sessions")</f>
+        <f>COUNTIF('User Stories'!B2:B104,"Sessions")</f>
         <v/>
       </c>
     </row>
@@ -6740,7 +6992,7 @@
         </is>
       </c>
       <c r="B22" s="12">
-        <f>COUNTIF('User Stories'!B2:B100,"CLI")</f>
+        <f>COUNTIF('User Stories'!B2:B104,"CLI")</f>
         <v/>
       </c>
     </row>
@@ -6751,7 +7003,7 @@
         </is>
       </c>
       <c r="B23" s="12">
-        <f>COUNTIF('User Stories'!B2:B100,"Collectors")</f>
+        <f>COUNTIF('User Stories'!B2:B104,"Collectors")</f>
         <v/>
       </c>
     </row>
@@ -6762,7 +7014,7 @@
         </is>
       </c>
       <c r="B24" s="12">
-        <f>COUNTIF('User Stories'!B2:B100,"Reporting")</f>
+        <f>COUNTIF('User Stories'!B2:B104,"Reporting")</f>
         <v/>
       </c>
     </row>
@@ -6773,7 +7025,7 @@
         </is>
       </c>
       <c r="B25" s="12">
-        <f>COUNTIF('User Stories'!B2:B100,"Config")</f>
+        <f>COUNTIF('User Stories'!B2:B104,"Config")</f>
         <v/>
       </c>
     </row>
@@ -6784,7 +7036,7 @@
         </is>
       </c>
       <c r="B26" s="12">
-        <f>COUNTIF('User Stories'!B2:B100,"Control Center")</f>
+        <f>COUNTIF('User Stories'!B2:B104,"Control Center")</f>
         <v/>
       </c>
     </row>
@@ -6795,7 +7047,7 @@
         </is>
       </c>
       <c r="B27" s="12">
-        <f>COUNTIF('User Stories'!B2:B100,"Extension Options")</f>
+        <f>COUNTIF('User Stories'!B2:B104,"Extension Options")</f>
         <v/>
       </c>
     </row>
@@ -6806,7 +7058,7 @@
         </is>
       </c>
       <c r="B28" s="12">
-        <f>COUNTIF('User Stories'!B2:B100,"Extension Popup")</f>
+        <f>COUNTIF('User Stories'!B2:B104,"Extension Popup")</f>
         <v/>
       </c>
     </row>
@@ -6817,7 +7069,7 @@
         </is>
       </c>
       <c r="B29" s="12">
-        <f>COUNTIF('User Stories'!B2:B100,"Extension Background")</f>
+        <f>COUNTIF('User Stories'!B2:B104,"Extension Background")</f>
         <v/>
       </c>
     </row>
@@ -6828,7 +7080,7 @@
         </is>
       </c>
       <c r="B30" s="12">
-        <f>COUNTIF('User Stories'!B2:B100,"Launcher")</f>
+        <f>COUNTIF('User Stories'!B2:B104,"Launcher")</f>
         <v/>
       </c>
     </row>
